--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$H$60</definedName>
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 13:40:28</t>
+          <t>2026-05-15 12:42:05</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Mixed ID formats (some coded, some bare numbers)</t>
+          <t>Mixed ID formats</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>29 coded vs 1 bare numbers</t>
+          <t>29 coded (e.g. CUST-001) vs 1 bare numbers</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Null: 3, Blank: 1, Whitespace: 1</t>
+          <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Null: 14, Blank: 1, Whitespace: 1</t>
+          <t>Null: 14, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$I$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -103,9 +108,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -488,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,35 +511,71 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>File:</t>
+          <t>Health Score:</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>sample_messy_data.xlsx</t>
+          <t>32/100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Audit Date:</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-15 12:42:05</t>
+          <t>File:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>sample_messy_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Audit Date:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:41:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Total Issues:</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Customers</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Score: 0/100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Orders</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Score: 65/100</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -547,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -558,2530 +600,2926 @@
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Inferred Type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Issue Type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Example / Detail</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Fix</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Mixed ID formats</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>29 coded (e.g. CUST-001) vs 1 bare numbers</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>df["_CustomerID_format"] = df["CustomerID"].apply(
+    lambda x: "coded" if isinstance(x, str)
+    and "-" in x else "numeric"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>df["FirstName"] = df["FirstName"].fillna(df["FirstName"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Code/ID stuffed in name field</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>REF-4421</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t># Review rows where FirstName contains unexpected data
+mask = df["FirstName"].notna()
+suspect = df.loc[mask, "FirstName"]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 3 times</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["FirstName"] = df["FirstName"].replace("Test", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["FirstName"] = df["FirstName"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>df["LastName"] = df["LastName"].fillna(df["LastName"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["LastName"] = df["LastName"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>"User" repeated 3 times</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>df["_LastName_review"] = (
+    df["LastName"] == "User"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>"Doe" repeated 3 times</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>df["_LastName_review"] = (
+    df["LastName"] == "Doe"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>df["Email"] = df["Email"].fillna(df["Email"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>henrylee</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
+df["_Email_invalid"] = ~df["Email"].str.match(
+    email_re, na=False
+)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>nancy w@example.com</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
+df["_Email_invalid"] = ~df["Email"].str.match(
+    email_re, na=False
+)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>"test@test.com" repeated 3 times</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>df["_Email_review"] = (
+    df["Email"] == "test@test.com"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>df["Phone"] = df["Phone"].fillna(df["Phone"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Mixed phone formats: 17 values deviate from (XXX) XXX-XXXX</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>(XXX) XXX-XXXX: 9; XXX-XXX-XXXX: 8; (non-standard): 3; +1-XXX-XXX-XXXX: 2; XXXXXXXXXX: 1; XXX.XXX.XXXX: 1; XXX XXX XXXX: 1; (XXX)XXXXXXX: 1</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Inconsistent phone formats break deduplication, prevent reliable search/lookup, and cause issues with automated dialers or SMS systems. Two records for the same person may appear as different contacts if one says "(555) 123-4567" and another says "5551234567".</t>
         </is>
       </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>digits = df["Phone"].str.replace(r"\D", "", regex=True)
+digits = digits.str.slice(-10)
+df["Phone"] = (
+    "(" + digits.str[:3] + ") "
+    + digits.str[3:6] + "-" + digits.str[6:]
+)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["Phone"] = df["Phone"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>"(555) 123-4567" repeated 3 times</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>df["_Phone_review"] = (
+    df["Phone"] == "(555) 123-4567"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>"000-000-0000" repeated 3 times</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>df["_Phone_review"] = (
+    df["Phone"] == "000-000-0000"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>"555-555-5555" repeated 3 times</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>df["_Phone_review"] = (
+    df["Phone"] == "555-555-5555"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>df["JoinDate"] = df["JoinDate"].fillna(df["JoinDate"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 12 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 14; MM/DD/YYYY: 3; Mon DD, YYYY: 3; (non-standard): 1; YYYY/MM/DD: 1; M/D/YYYY: 1; DD-Mon-YYYY: 1; YYYY.MM.DD: 1; MM-DD-YYYY: 1</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>df["JoinDate"] = pd.to_datetime(
+    df["JoinDate"], format="mixed", dayfirst=False
+).dt.strftime("%Y-%m-%d")</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["JoinDate"] = df["JoinDate"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>"2023-01-01" repeated 6 times</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>df["_JoinDate_review"] = (
+    df["JoinDate"] == "2023-01-01"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>"2023-01-15" repeated 3 times</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>df["_JoinDate_review"] = (
+    df["JoinDate"] == "2023-01-15"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>df["AccountBalance"] = df["AccountBalance"].fillna(df["AccountBalance"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats: 11 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 15; X,XXX.XX (no symbol): 4; $X,XXX: 3; (non-standard): 2; $X,XXX.XX USD: 2</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>df["AccountBalance"] = (
+    df["AccountBalance"].str.replace(r"[^\d.]", "", regex=True)
+    .astype(float)
+)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
+    r"^[\$\d,\.\-]+$", na=False
+)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>five thousand</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
+    r"^[\$\d,\.\-]+$", na=False
+)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["AccountBalance"] = df["AccountBalance"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>"$0.00" repeated 6 times</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>df["_AccountBalance_review"] = (
+    df["AccountBalance"] == "$0.00"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>"$1,250.00" repeated 3 times</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>df["_AccountBalance_review"] = (
+    df["AccountBalance"] == "$1,250.00"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>df["Status"] = df["Status"].fillna(df["Status"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE / Active / active</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t># Review rows where Status contains unexpected data
+mask = df["Status"].notna()
+suspect = df.loc[mask, "Status"]</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["Status"] = df["Status"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>"Active" repeated 18 times</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>69.2% of non-null values</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>df["_Status_review"] = (
+    df["Status"] == "Active"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>df["ZipCode"] = df["ZipCode"].fillna(df["ZipCode"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Placeholder "00000" found 3 times</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["ZipCode"] = df["ZipCode"].replace("00000", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["ZipCode"] = df["ZipCode"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>"30301" repeated 3 times</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>df["_ZipCode_review"] = (
+    df["ZipCode"] == "30301"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>"12345" repeated 3 times</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>df["_ZipCode_review"] = (
+    df["ZipCode"] == "12345"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>15 of 30 values missing (50.0%)</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Null: 14, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t># Option A: Fill with most common value
+df["Notes"] = df["Notes"].fillna(df["Notes"].mode()[0])
+# Option B: Fill with a sentinel
+df["Notes"] = df["Notes"].fillna("MISSING")</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TEST" found 3 times</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["Notes"] = df["Notes"].replace("TEST", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>6.7% of non-null values</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["Notes"] = df["Notes"].replace("TBD", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>"Preferred customer" repeated 3 times</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>df["_Notes_review"] = (
+    df["Notes"] == "Preferred customer"
+)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Rows: 2, 8, 9</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t># Normalize text columns before deduplication
+text_cols = df.select_dtypes(include="object").columns
+for col in text_cols:
+    df[col] = df[col].str.strip().str.lower()
+df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Rows: 3, 10</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t># Normalize text columns before deduplication
+text_cols = df.select_dtypes(include="object").columns
+for col in text_cols:
+    df[col] = df[col].str.strip().str.lower()
+df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Rows: 11, 12, 13</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>4 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Rows: 14, 19, 20, 21</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t># Normalize text columns before deduplication
+text_cols = df.select_dtypes(include="object").columns
+for col in text_cols:
+    df[col] = df[col].str.strip().str.lower()
+df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Rows: 25, 27</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>OrderDate</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 4 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 6; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1; YYYY/MM/DD: 1</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>df["OrderDate"] = pd.to_datetime(
+    df["OrderDate"], format="mixed", dayfirst=False
+).dt.strftime("%Y-%m-%d")</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats: 3 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 7; X,XXX (bare number): 2; $X,XXX: 1</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>df["Amount"] = (
+    df["Amount"].str.replace(r"[^\d.]", "", regex=True)
+    .astype(float)
+)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>2 of 10 values missing (20.0%)</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Null: 2, Blank: 0, Whitespace: 0</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>df["ShipDate"] = df["ShipDate"].fillna(df["ShipDate"].mode()[0])</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 3 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 5; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>df["ShipDate"] = pd.to_datetime(
+    df["ShipDate"], format="mixed", dayfirst=False
+).dt.strftime("%Y-%m-%d")</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Shipped / shipped</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t># Review rows where Status contains unexpected data
+mask = df["Status"].notna()
+suspect = df.loc[mask, "Status"]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Delivered / delivered</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t># Review rows where Status contains unexpected data
+mask = df["Status"].notna()
+suspect = df.loc[mask, "Status"]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>PENDING / Pending</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t># Review rows where Status contains unexpected data
+mask = df["Status"].notna()
+suspect = df.loc[mask, "Status"]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 2 times</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>import numpy as np
+df["Status"] = df["Status"].replace("Test", np.nan)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Rows: 5, 6</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Rows: 7, 8</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H60"/>
+  <autoFilter ref="A1:I60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15 14:41:31</t>
+          <t>2026-05-15 15:03:29</t>
         </is>
       </c>
     </row>
@@ -575,6 +575,49 @@
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Score: 65/100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Trend vs Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Baseline:</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>sample_messy_data.xlsx (2026-05-15 15:03:07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Score Change:</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>28 → 32 (+4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Issues Change:</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>63 → 59 (-4)</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15 15:03:29</t>
+          <t>2026-05-16 12:00:51</t>
         </is>
       </c>
     </row>
@@ -575,49 +575,6 @@
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Score: 65/100</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Trend vs Baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Baseline:</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>sample_messy_data.xlsx (2026-05-15 15:03:07)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Score Change:</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>28 → 32 (+4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Issues Change:</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>63 → 59 (-4)</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,28 +29,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Source Sans Pro"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Source Sans Pro"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Source Sans Pro"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Source Sans Pro"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Source Sans Pro"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -63,22 +67,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000f3460"/>
+        <fgColor rgb="001f2e7a"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00fce8e7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00e4f5f0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00fdeee0"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,27 +96,28 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00cccccc"/>
+        <color rgb="00d9d9d9"/>
       </left>
       <right style="thin">
-        <color rgb="00cccccc"/>
+        <color rgb="00d9d9d9"/>
       </right>
       <top style="thin">
-        <color rgb="00cccccc"/>
+        <color rgb="00d9d9d9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00cccccc"/>
+        <color rgb="00d9d9d9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -540,7 +545,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16 12:00:51</t>
+          <t>2026-05-20 11:12:08</t>
         </is>
       </c>
     </row>
@@ -560,7 +565,7 @@
           <t>Sheet: Customers</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Score: 0/100</t>
         </is>
@@ -572,7 +577,7 @@
           <t>Sheet: Orders</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Score: 65/100</t>
         </is>
@@ -604,94 +609,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Inferred Type</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Issue Type</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Example / Detail</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Mixed ID formats</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>29 coded (e.g. CUST-001) vs 1 bare numbers</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>df["_CustomerID_format"] = df["CustomerID"].apply(
     lambda x: "coded" if isinstance(x, str)
@@ -701,94 +706,94 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>df["FirstName"] = df["FirstName"].fillna(df["FirstName"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Code/ID stuffed in name field</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>REF-4421</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t># Review rows where FirstName contains unexpected data
 mask = df["FirstName"].notna()
@@ -797,47 +802,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 3 times</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["FirstName"] = df["FirstName"].replace("Test", np.nan)</t>
@@ -845,47 +850,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["FirstName"] = df["FirstName"].replace("TBD", np.nan)</t>
@@ -893,94 +898,94 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>df["LastName"] = df["LastName"].fillna(df["LastName"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["LastName"] = df["LastName"].replace("TBD", np.nan)</t>
@@ -988,47 +993,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>"User" repeated 3 times</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>df["_LastName_review"] = (
     df["LastName"] == "User"
@@ -1037,47 +1042,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>"Doe" repeated 3 times</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>df["_LastName_review"] = (
     df["LastName"] == "Doe"
@@ -1086,94 +1091,94 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>df["Email"] = df["Email"].fillna(df["Email"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>henrylee</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
 df["_Email_invalid"] = ~df["Email"].str.match(
@@ -1183,47 +1188,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>nancy w@example.com</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
 df["_Email_invalid"] = ~df["Email"].str.match(
@@ -1233,47 +1238,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>"test@test.com" repeated 3 times</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>df["_Email_review"] = (
     df["Email"] == "test@test.com"
@@ -1282,94 +1287,94 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>df["Phone"] = df["Phone"].fillna(df["Phone"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Mixed phone formats: 17 values deviate from (XXX) XXX-XXXX</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>(XXX) XXX-XXXX: 9; XXX-XXX-XXXX: 8; (non-standard): 3; +1-XXX-XXX-XXXX: 2; XXXXXXXXXX: 1; XXX.XXX.XXXX: 1; XXX XXX XXXX: 1; (XXX)XXXXXXX: 1</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Inconsistent phone formats break deduplication, prevent reliable search/lookup, and cause issues with automated dialers or SMS systems. Two records for the same person may appear as different contacts if one says "(555) 123-4567" and another says "5551234567".</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>digits = df["Phone"].str.replace(r"\D", "", regex=True)
 digits = digits.str.slice(-10)
@@ -1381,47 +1386,47 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Phone"] = df["Phone"].replace("TBD", np.nan)</t>
@@ -1429,47 +1434,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>"(555) 123-4567" repeated 3 times</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "(555) 123-4567"
@@ -1478,47 +1483,47 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>"000-000-0000" repeated 3 times</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "000-000-0000"
@@ -1527,47 +1532,47 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>"555-555-5555" repeated 3 times</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "555-555-5555"
@@ -1576,94 +1581,94 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>df["JoinDate"] = df["JoinDate"].fillna(df["JoinDate"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats: 12 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 14; MM/DD/YYYY: 3; Mon DD, YYYY: 3; (non-standard): 1; YYYY/MM/DD: 1; M/D/YYYY: 1; DD-Mon-YYYY: 1; YYYY.MM.DD: 1; MM-DD-YYYY: 1</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>df["JoinDate"] = pd.to_datetime(
     df["JoinDate"], format="mixed", dayfirst=False
@@ -1672,47 +1677,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["JoinDate"] = df["JoinDate"].replace("TBD", np.nan)</t>
@@ -1720,47 +1725,47 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>"2023-01-01" repeated 6 times</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>df["_JoinDate_review"] = (
     df["JoinDate"] == "2023-01-01"
@@ -1769,47 +1774,47 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>"2023-01-15" repeated 3 times</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>df["_JoinDate_review"] = (
     df["JoinDate"] == "2023-01-15"
@@ -1818,94 +1823,94 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>df["AccountBalance"] = df["AccountBalance"].fillna(df["AccountBalance"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Mixed currency formats: 11 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 15; X,XXX.XX (no symbol): 4; $X,XXX: 3; (non-standard): 2; $X,XXX.XX USD: 2</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>df["AccountBalance"] = (
     df["AccountBalance"].str.replace(r"[^\d.]", "", regex=True)
@@ -1915,47 +1920,47 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
     r"^[\$\d,\.\-]+$", na=False
@@ -1964,47 +1969,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>five thousand</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
     r"^[\$\d,\.\-]+$", na=False
@@ -2013,47 +2018,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["AccountBalance"] = df["AccountBalance"].replace("TBD", np.nan)</t>
@@ -2061,47 +2066,47 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>"$0.00" repeated 6 times</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>df["_AccountBalance_review"] = (
     df["AccountBalance"] == "$0.00"
@@ -2110,47 +2115,47 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>"$1,250.00" repeated 3 times</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>df["_AccountBalance_review"] = (
     df["AccountBalance"] == "$1,250.00"
@@ -2159,94 +2164,94 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>df["Status"] = df["Status"].fillna(df["Status"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / Active / active</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -2255,47 +2260,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Status"] = df["Status"].replace("TBD", np.nan)</t>
@@ -2303,47 +2308,47 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>"Active" repeated 18 times</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>69.2% of non-null values</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>df["_Status_review"] = (
     df["Status"] == "Active"
@@ -2352,94 +2357,94 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>df["ZipCode"] = df["ZipCode"].fillna(df["ZipCode"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Placeholder "00000" found 3 times</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["ZipCode"] = df["ZipCode"].replace("00000", np.nan)</t>
@@ -2447,47 +2452,47 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["ZipCode"] = df["ZipCode"].replace("TBD", np.nan)</t>
@@ -2495,47 +2500,47 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>"30301" repeated 3 times</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>df["_ZipCode_review"] = (
     df["ZipCode"] == "30301"
@@ -2544,47 +2549,47 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>"12345" repeated 3 times</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>df["_ZipCode_review"] = (
     df["ZipCode"] == "12345"
@@ -2593,47 +2598,47 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>15 of 30 values missing (50.0%)</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>Null: 14, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t># Option A: Fill with most common value
 df["Notes"] = df["Notes"].fillna(df["Notes"].mode()[0])
@@ -2643,47 +2648,47 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TEST" found 3 times</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Notes"] = df["Notes"].replace("TEST", np.nan)</t>
@@ -2691,47 +2696,47 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>6.7% of non-null values</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Notes"] = df["Notes"].replace("TBD", np.nan)</t>
@@ -2739,47 +2744,47 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>"Preferred customer" repeated 3 times</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>df["_Notes_review"] = (
     df["Notes"] == "Preferred customer"
@@ -2788,47 +2793,47 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Rows: 2, 8, 9</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2839,47 +2844,47 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>Rows: 3, 10</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2890,94 +2895,94 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>Rows: 11, 12, 13</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>4 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Rows: 14, 19, 20, 21</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2988,94 +2993,94 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Rows: 25, 27</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>OrderDate</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats: 4 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 6; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1; YYYY/MM/DD: 1</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>df["OrderDate"] = pd.to_datetime(
     df["OrderDate"], format="mixed", dayfirst=False
@@ -3084,47 +3089,47 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Mixed currency formats: 3 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 7; X,XXX (bare number): 2; $X,XXX: 1</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>df["Amount"] = (
     df["Amount"].str.replace(r"[^\d.]", "", regex=True)
@@ -3134,94 +3139,94 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>2 of 10 values missing (20.0%)</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Null: 2, Blank: 0, Whitespace: 0</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>df["ShipDate"] = df["ShipDate"].fillna(df["ShipDate"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats: 3 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 5; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>df["ShipDate"] = pd.to_datetime(
     df["ShipDate"], format="mixed", dayfirst=False
@@ -3230,47 +3235,47 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Shipped / shipped</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3279,47 +3284,47 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>Delivered / delivered</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3328,47 +3333,47 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>PENDING / Pending</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3377,47 +3382,47 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 2 times</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Status"] = df["Status"].replace("Test", np.nan)</t>
@@ -3425,94 +3430,94 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>Rows: 5, 6</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Rows: 7, 8</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,10 +51,6 @@
     <font>
       <name val="Source Sans Pro"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -112,12 +108,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -545,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20 11:12:08</t>
+          <t>2026-05-20 11:28:11</t>
         </is>
       </c>
     </row>
@@ -565,7 +560,7 @@
           <t>Sheet: Customers</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Score: 0/100</t>
         </is>
@@ -577,7 +572,7 @@
           <t>Sheet: Orders</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Score: 65/100</t>
         </is>
@@ -609,94 +604,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Inferred Type</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Issue Type</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Example / Detail</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Mixed ID formats</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>29 coded (e.g. CUST-001) vs 1 bare numbers</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>df["_CustomerID_format"] = df["CustomerID"].apply(
     lambda x: "coded" if isinstance(x, str)
@@ -706,94 +701,94 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>df["FirstName"] = df["FirstName"].fillna(df["FirstName"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Code/ID stuffed in name field</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>REF-4421</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t># Review rows where FirstName contains unexpected data
 mask = df["FirstName"].notna()
@@ -802,47 +797,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 3 times</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["FirstName"] = df["FirstName"].replace("Test", np.nan)</t>
@@ -850,47 +845,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["FirstName"] = df["FirstName"].replace("TBD", np.nan)</t>
@@ -898,94 +893,94 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>df["LastName"] = df["LastName"].fillna(df["LastName"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["LastName"] = df["LastName"].replace("TBD", np.nan)</t>
@@ -993,47 +988,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>"User" repeated 3 times</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>df["_LastName_review"] = (
     df["LastName"] == "User"
@@ -1042,47 +1037,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>"Doe" repeated 3 times</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>df["_LastName_review"] = (
     df["LastName"] == "Doe"
@@ -1091,94 +1086,94 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>df["Email"] = df["Email"].fillna(df["Email"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>henrylee</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
 df["_Email_invalid"] = ~df["Email"].str.match(
@@ -1188,47 +1183,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>nancy w@example.com</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>email_re = r"^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$"
 df["_Email_invalid"] = ~df["Email"].str.match(
@@ -1238,47 +1233,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>"test@test.com" repeated 3 times</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>df["_Email_review"] = (
     df["Email"] == "test@test.com"
@@ -1287,94 +1282,94 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>df["Phone"] = df["Phone"].fillna(df["Phone"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Mixed phone formats: 17 values deviate from (XXX) XXX-XXXX</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>(XXX) XXX-XXXX: 9; XXX-XXX-XXXX: 8; (non-standard): 3; +1-XXX-XXX-XXXX: 2; XXXXXXXXXX: 1; XXX.XXX.XXXX: 1; XXX XXX XXXX: 1; (XXX)XXXXXXX: 1</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Inconsistent phone formats break deduplication, prevent reliable search/lookup, and cause issues with automated dialers or SMS systems. Two records for the same person may appear as different contacts if one says "(555) 123-4567" and another says "5551234567".</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>digits = df["Phone"].str.replace(r"\D", "", regex=True)
 digits = digits.str.slice(-10)
@@ -1386,47 +1381,47 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Phone"] = df["Phone"].replace("TBD", np.nan)</t>
@@ -1434,47 +1429,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>"(555) 123-4567" repeated 3 times</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "(555) 123-4567"
@@ -1483,47 +1478,47 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>"000-000-0000" repeated 3 times</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "000-000-0000"
@@ -1532,47 +1527,47 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>"555-555-5555" repeated 3 times</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>df["_Phone_review"] = (
     df["Phone"] == "555-555-5555"
@@ -1581,94 +1576,94 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>df["JoinDate"] = df["JoinDate"].fillna(df["JoinDate"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 12 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 14; MM/DD/YYYY: 3; Mon DD, YYYY: 3; (non-standard): 1; YYYY/MM/DD: 1; M/D/YYYY: 1; DD-Mon-YYYY: 1; YYYY.MM.DD: 1; MM-DD-YYYY: 1</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>df["JoinDate"] = pd.to_datetime(
     df["JoinDate"], format="mixed", dayfirst=False
@@ -1677,47 +1672,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["JoinDate"] = df["JoinDate"].replace("TBD", np.nan)</t>
@@ -1725,47 +1720,47 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>"2023-01-01" repeated 6 times</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>df["_JoinDate_review"] = (
     df["JoinDate"] == "2023-01-01"
@@ -1774,47 +1769,47 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>JoinDate</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>"2023-01-15" repeated 3 times</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>df["_JoinDate_review"] = (
     df["JoinDate"] == "2023-01-15"
@@ -1823,94 +1818,94 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>df["AccountBalance"] = df["AccountBalance"].fillna(df["AccountBalance"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats: 11 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 15; X,XXX.XX (no symbol): 4; $X,XXX: 3; (non-standard): 2; $X,XXX.XX USD: 2</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>df["AccountBalance"] = (
     df["AccountBalance"].str.replace(r"[^\d.]", "", regex=True)
@@ -1920,47 +1915,47 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
     r"^[\$\d,\.\-]+$", na=False
@@ -1969,47 +1964,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Text in currency field</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>five thousand</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>df["_AccountBalance_invalid"] = ~df["AccountBalance"].str.match(
     r"^[\$\d,\.\-]+$", na=False
@@ -2018,47 +2013,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["AccountBalance"] = df["AccountBalance"].replace("TBD", np.nan)</t>
@@ -2066,47 +2061,47 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>"$0.00" repeated 6 times</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>23.1% of non-null values</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>df["_AccountBalance_review"] = (
     df["AccountBalance"] == "$0.00"
@@ -2115,47 +2110,47 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>AccountBalance</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>"$1,250.00" repeated 3 times</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>df["_AccountBalance_review"] = (
     df["AccountBalance"] == "$1,250.00"
@@ -2164,94 +2159,94 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>df["Status"] = df["Status"].fillna(df["Status"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE / Active / active</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -2260,47 +2255,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Status"] = df["Status"].replace("TBD", np.nan)</t>
@@ -2308,47 +2303,47 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>"Active" repeated 18 times</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>69.2% of non-null values</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>df["_Status_review"] = (
     df["Status"] == "Active"
@@ -2357,94 +2352,94 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>4 of 30 values missing (13.3%)</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Null: 3, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>df["ZipCode"] = df["ZipCode"].fillna(df["ZipCode"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Placeholder "00000" found 3 times</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["ZipCode"] = df["ZipCode"].replace("00000", np.nan)</t>
@@ -2452,47 +2447,47 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>3.8% of non-null values</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["ZipCode"] = df["ZipCode"].replace("TBD", np.nan)</t>
@@ -2500,47 +2495,47 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>"30301" repeated 3 times</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>df["_ZipCode_review"] = (
     df["ZipCode"] == "30301"
@@ -2549,47 +2544,47 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>ZipCode</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>zipcode</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>"12345" repeated 3 times</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>11.5% of non-null values</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>df["_ZipCode_review"] = (
     df["ZipCode"] == "12345"
@@ -2598,47 +2593,47 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>15 of 30 values missing (50.0%)</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Null: 14, Blank: 0, Whitespace: 1</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t># Option A: Fill with most common value
 df["Notes"] = df["Notes"].fillna(df["Notes"].mode()[0])
@@ -2648,47 +2643,47 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TEST" found 3 times</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Notes"] = df["Notes"].replace("TEST", np.nan)</t>
@@ -2696,47 +2691,47 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Placeholder "TBD" found 1 times</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>6.7% of non-null values</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Notes"] = df["Notes"].replace("TBD", np.nan)</t>
@@ -2744,47 +2739,47 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>freetext</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>suspicious_repetition</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>"Preferred customer" repeated 3 times</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>When the same value appears far more often than expected, it may indicate a default value that was never updated, a copy-paste error, or a system glitch that stamped the same data across multiple records.</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>df["_Notes_review"] = (
     df["Notes"] == "Preferred customer"
@@ -2793,47 +2788,47 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Rows: 2, 8, 9</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2844,47 +2839,47 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Rows: 3, 10</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2895,94 +2890,94 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>3 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Rows: 11, 12, 13</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Phantom Duplicate</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>4 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Rows: 14, 19, 20, 21</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>These records look different on the surface (different casing, extra spaces, punctuation variations) but represent the same entity. They cause inflated counts, split transaction histories, and duplicate outreach — problems that compound over time.</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t># Normalize text columns before deduplication
 text_cols = df.select_dtypes(include="object").columns
@@ -2993,94 +2988,94 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Rows: 25, 27</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>OrderDate</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 4 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 6; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1; YYYY/MM/DD: 1</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>df["OrderDate"] = pd.to_datetime(
     df["OrderDate"], format="mixed", dayfirst=False
@@ -3089,47 +3084,47 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats: 3 values deviate from $X,XXX.XX</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>$X,XXX.XX: 7; X,XXX (bare number): 2; $X,XXX: 1</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Mixed currency formats ("$1,250.00" vs "1250" vs "five thousand") prevent accurate aggregation and comparison. Summing a column with text-formatted currency returns errors or silently drops values, leading to wrong totals in financial reports.</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>df["Amount"] = (
     df["Amount"].str.replace(r"[^\d.]", "", regex=True)
@@ -3139,94 +3134,94 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>null_analysis</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>2 of 10 values missing (20.0%)</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Null: 2, Blank: 0, Whitespace: 0</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>High rates of missing data reduce the reliability of any analysis built on this field. Missing values can skew averages, break joins between tables, and cause downstream systems to error out or produce incomplete results.</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>df["ShipDate"] = df["ShipDate"].fillna(df["ShipDate"].mode()[0])</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>ShipDate</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>mixed_format</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats: 3 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>YYYY-MM-DD: 5; MM/DD/YYYY: 1; Mon DD, YYYY: 1; M/D/YYYY: 1</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Mixed date formats cause sorting failures, broken filters, and incorrect calculations. A date stored as text ("Jan 15, 2023") won't sort chronologically next to "2023-01-15". Downstream tools, APIs, and reports will misparse or reject inconsistent dates.</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>df["ShipDate"] = pd.to_datetime(
     df["ShipDate"], format="mixed", dayfirst=False
@@ -3235,47 +3230,47 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Shipped / shipped</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3284,47 +3279,47 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Delivered / delivered</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3333,47 +3328,47 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>wrong_purpose</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Inconsistent casing in categorical values</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>PENDING / Pending</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t># Review rows where Status contains unexpected data
 mask = df["Status"].notna()
@@ -3382,47 +3377,47 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>placeholder_value</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Placeholder "Test" found 2 times</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>20.0% of non-null values</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Placeholder values ("Test", "N/A", "TBD") that persist in production data inflate counts, skew averages, and create phantom records. They often indicate incomplete data entry or inadequate validation at the point of capture.</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>import numpy as np
 df["Status"] = df["Status"].replace("Test", np.nan)</t>
@@ -3430,94 +3425,94 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Rows: 5, 6</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>(row-level)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Exact Duplicate</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>2 rows appear to be the same record</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Rows: 7, 8</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Exact duplicate rows are the clearest sign of a data quality issue — they can result from double-submissions, ETL failures, or missing unique constraints. Every duplicate inflates counts and distorts any metric built on this data.</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>df = df.drop_duplicates(keep="first").reset_index(drop=True)</t>
         </is>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20 11:28:11</t>
+          <t>2026-07-07 18:48:43</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,16 @@
           <t>Suggested Fix</t>
         </is>
       </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Cardinality</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Uniqueness %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -688,7 +698,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>When a field is used for something other than its intended purpose — like storing reference codes in a name field or text in a currency field — it corrupts both the misused field and whatever field should have held that data. This makes the data unreliable for any analysis.</t>
+          <t>Inconsistent ID formats break joins, lookups, and deduplication — a key stored as "CUST-001" won't match "1027", so related records silently fail to link.</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -699,6 +709,12 @@
 )</t>
         </is>
       </c>
+      <c r="J2" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -745,6 +761,12 @@
         <is>
           <t>df["FirstName"] = df["FirstName"].fillna(df["FirstName"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>80.8</v>
       </c>
     </row>
     <row r="4">
@@ -795,6 +817,12 @@
 suspect = df.loc[mask, "FirstName"]</t>
         </is>
       </c>
+      <c r="J4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -843,6 +871,12 @@
 df["FirstName"] = df["FirstName"].replace("Test", np.nan)</t>
         </is>
       </c>
+      <c r="J5" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -891,6 +925,12 @@
 df["FirstName"] = df["FirstName"].replace("TBD", np.nan)</t>
         </is>
       </c>
+      <c r="J6" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -938,6 +978,12 @@
           <t>df["LastName"] = df["LastName"].fillna(df["LastName"].mode()[0])</t>
         </is>
       </c>
+      <c r="J7" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>76.90000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -985,6 +1031,12 @@
           <t>import numpy as np
 df["LastName"] = df["LastName"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1035,6 +1087,12 @@
 )</t>
         </is>
       </c>
+      <c r="J9" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>76.90000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1084,6 +1142,12 @@
 )</t>
         </is>
       </c>
+      <c r="J10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>76.90000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1130,6 +1194,12 @@
         <is>
           <t>df["Email"] = df["Email"].fillna(df["Email"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>80.8</v>
       </c>
     </row>
     <row r="12">
@@ -1181,6 +1251,12 @@
 )</t>
         </is>
       </c>
+      <c r="J12" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1231,6 +1307,12 @@
 )</t>
         </is>
       </c>
+      <c r="J13" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1280,6 +1362,12 @@
 )</t>
         </is>
       </c>
+      <c r="J14" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1326,6 +1414,12 @@
         <is>
           <t>df["Phone"] = df["Phone"].fillna(df["Phone"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1379,6 +1473,12 @@
 )</t>
         </is>
       </c>
+      <c r="J16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1426,6 +1526,12 @@
           <t>import numpy as np
 df["Phone"] = df["Phone"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1476,6 +1582,12 @@
 )</t>
         </is>
       </c>
+      <c r="J18" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1525,6 +1637,12 @@
 )</t>
         </is>
       </c>
+      <c r="J19" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1574,6 +1692,12 @@
 )</t>
         </is>
       </c>
+      <c r="J20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1620,6 +1744,12 @@
         <is>
           <t>df["JoinDate"] = df["JoinDate"].fillna(df["JoinDate"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="22">
@@ -1670,6 +1800,12 @@
 ).dt.strftime("%Y-%m-%d")</t>
         </is>
       </c>
+      <c r="J22" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1717,6 +1853,12 @@
           <t>import numpy as np
 df["JoinDate"] = df["JoinDate"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="24">
@@ -1767,6 +1909,12 @@
 )</t>
         </is>
       </c>
+      <c r="J24" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1816,6 +1964,12 @@
 )</t>
         </is>
       </c>
+      <c r="J25" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1862,6 +2016,12 @@
         <is>
           <t>df["AccountBalance"] = df["AccountBalance"].fillna(df["AccountBalance"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="27">
@@ -1913,6 +2073,12 @@
 )</t>
         </is>
       </c>
+      <c r="J27" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1962,6 +2128,12 @@
 )</t>
         </is>
       </c>
+      <c r="J28" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2011,6 +2183,12 @@
 )</t>
         </is>
       </c>
+      <c r="J29" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -2058,6 +2236,12 @@
           <t>import numpy as np
 df["AccountBalance"] = df["AccountBalance"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="31">
@@ -2108,6 +2292,12 @@
 )</t>
         </is>
       </c>
+      <c r="J31" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2157,6 +2347,12 @@
 )</t>
         </is>
       </c>
+      <c r="J32" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2203,6 +2399,12 @@
         <is>
           <t>df["Status"] = df["Status"].fillna(df["Status"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="34">
@@ -2253,6 +2455,12 @@
 suspect = df.loc[mask, "Status"]</t>
         </is>
       </c>
+      <c r="J34" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>30.8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2300,6 +2508,12 @@
           <t>import numpy as np
 df["Status"] = df["Status"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="36">
@@ -2350,6 +2564,12 @@
 )</t>
         </is>
       </c>
+      <c r="J36" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>30.8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2397,6 +2617,12 @@
           <t>df["ZipCode"] = df["ZipCode"].fillna(df["ZipCode"].mode()[0])</t>
         </is>
       </c>
+      <c r="J37" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2445,6 +2671,12 @@
 df["ZipCode"] = df["ZipCode"].replace("00000", np.nan)</t>
         </is>
       </c>
+      <c r="J38" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2492,6 +2724,12 @@
           <t>import numpy as np
 df["ZipCode"] = df["ZipCode"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2542,6 +2780,12 @@
 )</t>
         </is>
       </c>
+      <c r="J40" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2590,6 +2834,12 @@
     df["ZipCode"] == "12345"
 )</t>
         </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2641,6 +2891,12 @@
 df["Notes"] = df["Notes"].fillna("MISSING")</t>
         </is>
       </c>
+      <c r="J42" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>73.3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2689,6 +2945,12 @@
 df["Notes"] = df["Notes"].replace("TEST", np.nan)</t>
         </is>
       </c>
+      <c r="J43" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>73.3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2736,6 +2998,12 @@
           <t>import numpy as np
 df["Notes"] = df["Notes"].replace("TBD", np.nan)</t>
         </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>73.3</v>
       </c>
     </row>
     <row r="45">
@@ -2785,6 +3053,12 @@
     df["Notes"] == "Preferred customer"
 )</t>
         </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>73.3</v>
       </c>
     </row>
     <row r="46">
@@ -3082,6 +3356,12 @@
 ).dt.strftime("%Y-%m-%d")</t>
         </is>
       </c>
+      <c r="J51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -3132,6 +3412,12 @@
 )</t>
         </is>
       </c>
+      <c r="J52" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -3178,6 +3464,12 @@
         <is>
           <t>df["ShipDate"] = df["ShipDate"].fillna(df["ShipDate"].mode()[0])</t>
         </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="54">
@@ -3228,6 +3520,12 @@
 ).dt.strftime("%Y-%m-%d")</t>
         </is>
       </c>
+      <c r="J54" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -3277,6 +3575,12 @@
 suspect = df.loc[mask, "Status"]</t>
         </is>
       </c>
+      <c r="J55" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -3326,6 +3630,12 @@
 suspect = df.loc[mask, "Status"]</t>
         </is>
       </c>
+      <c r="J56" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -3375,6 +3685,12 @@
 suspect = df.loc[mask, "Status"]</t>
         </is>
       </c>
+      <c r="J57" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -3422,6 +3738,12 @@
           <t>import numpy as np
 df["Status"] = df["Status"].replace("Test", np.nan)</t>
         </is>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="59">

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>32/100</t>
+          <t>42/100</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:48:43</t>
+          <t>2026-07-08 15:09:34</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Score: 0/100</t>
+          <t>Score: 18/100</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 15:09:34</t>
+          <t>2026-07-14 19:29:16</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14 19:29:16</t>
+          <t>2026-07-15 09:02:00</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$I$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$K$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15 09:02:00</t>
+          <t>2026-07-27 16:58:34</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Mixed ID formats</t>
+          <t>Mixed ID formats: e.g. "29 coded (e.g. CUST-001) vs 1 bare numbers"</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Code/ID stuffed in name field</t>
+          <t>Code/ID stuffed in name field: e.g. "REF-4421"</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "Test" found 3 times</t>
+          <t>Placeholder: "Test" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>"User" repeated 3 times</t>
+          <t>Suspicious repetition: "User" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>"Doe" repeated 3 times</t>
+          <t>Suspicious repetition: "Doe" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Invalid email format: e.g. "henrylee"</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Invalid email format: e.g. "nancy w@example.com"</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>"test@test.com" repeated 3 times</t>
+          <t>Suspicious repetition: "test@test.com" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Mixed phone formats: 17 values deviate from (XXX) XXX-XXXX</t>
+          <t>Mixed phone formats: 17 of 26 values deviate from (XXX) XXX-XXXX</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>"(555) 123-4567" repeated 3 times</t>
+          <t>Suspicious repetition: "(555) 123-4567" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>"000-000-0000" repeated 3 times</t>
+          <t>Suspicious repetition: "000-000-0000" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>"555-555-5555" repeated 3 times</t>
+          <t>Suspicious repetition: "555-555-5555" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Mixed date formats: 12 values deviate from YYYY-MM-DD</t>
+          <t>Mixed date formats: 12 of 26 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>"2023-01-01" repeated 6 times</t>
+          <t>Suspicious repetition: "2023-01-01" appears 6 times (23.1%)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>"2023-01-15" repeated 3 times</t>
+          <t>Suspicious repetition: "2023-01-15" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Mixed currency formats: 11 values deviate from $X,XXX.XX</t>
+          <t>Mixed currency formats: 11 of 26 values deviate from $X,XXX.XX</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Text in currency field</t>
+          <t>Text in currency field: e.g. "TBD"</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Text in currency field</t>
+          <t>Text in currency field: e.g. "five thousand"</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>"$0.00" repeated 6 times</t>
+          <t>Suspicious repetition: "$0.00" appears 6 times (23.1%)</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>"$1,250.00" repeated 3 times</t>
+          <t>Suspicious repetition: "$1,250.00" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent casing in categorical values</t>
+          <t>Inconsistent casing in categorical values: e.g. "ACTIVE / Active / active"</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>"Active" repeated 18 times</t>
+          <t>Suspicious repetition: "Active" appears 18 times (69.2%)</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>4 of 30 values missing (13.3%)</t>
+          <t>High missing rate: 4 of 30 values missing (13.3%)</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "00000" found 3 times</t>
+          <t>Placeholder: "00000" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (3.8%)</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>"30301" repeated 3 times</t>
+          <t>Suspicious repetition: "30301" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>"12345" repeated 3 times</t>
+          <t>Suspicious repetition: "12345" appears 3 times (11.5%)</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>15 of 30 values missing (50.0%)</t>
+          <t>High missing rate: 15 of 30 values missing (50.0%)</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TEST" found 3 times</t>
+          <t>Placeholder: "TEST" appears 3 times (20.0%)</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (6.7%)</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>"Preferred customer" repeated 3 times</t>
+          <t>Suspicious repetition: "Preferred customer" appears 3 times (20.0%)</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Mixed date formats: 4 values deviate from YYYY-MM-DD</t>
+          <t>Mixed date formats: 4 of 10 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Mixed currency formats: 3 values deviate from $X,XXX.XX</t>
+          <t>Mixed currency formats: 3 of 10 values deviate from $X,XXX.XX</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>2 of 10 values missing (20.0%)</t>
+          <t>High missing rate: 2 of 10 values missing (20.0%)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Mixed date formats: 3 values deviate from YYYY-MM-DD</t>
+          <t>Mixed date formats: 3 of 8 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent casing in categorical values</t>
+          <t>Inconsistent casing in categorical values: e.g. "Shipped / shipped"</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent casing in categorical values</t>
+          <t>Inconsistent casing in categorical values: e.g. "Delivered / delivered"</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent casing in categorical values</t>
+          <t>Inconsistent casing in categorical values: e.g. "PENDING / Pending"</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "Test" found 2 times</t>
+          <t>Placeholder: "Test" appears 2 times (20.0%)</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I60"/>
+  <autoFilter ref="A1:K60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27 16:58:34</t>
+          <t>2026-07-31 21:22:51</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_messy_data_audit_findings.xlsx
+++ b/samples/output/sample_messy_data_audit_findings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$K$60</definedName>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27 16:58:34</t>
+          <t>2026-08-05 20:45:07</t>
         </is>
       </c>
     </row>
